--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>65.21807484317543</v>
+        <v>57.3318839375</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -580,11 +580,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>19.28486480640277</v>
+        <v>-0.652585000000002</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
-        <v>57.342585</v>
+        <v>65.21807484317543</v>
       </c>
       <c r="F4" t="n">
-        <v>71.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-0.652585000000002</v>
+        <v>24.68678996322734</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>65.21807484317543</v>
+        <v>65.27425830712657</v>
       </c>
       <c r="F4" t="n">
         <v>75.09999999999999</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="n">
         <v>65.27425830712657</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>24.68678996322734</v>
+        <v>29.80253165610077</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,47 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABBV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>262.395</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>65.27425830712657</v>
+        <v>262.395</v>
       </c>
       <c r="F4" t="n">
-        <v>75.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -624,11 +624,8 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>29.80253165610077</v>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -639,7 +636,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,13 +650,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
-        <v>262.395</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>75.3</v>
+        <v>71.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -668,10 +665,95 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SPYD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>95</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.33711741009385</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>29.80253165610077</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>increase toward target 15% of capital (core)</t>
         </is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>57.3318839375</v>
+        <v>262.395</v>
       </c>
       <c r="F3" t="n">
-        <v>71.2</v>
+        <v>75.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -580,11 +580,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-0.652585000000002</v>
+        <v>2.910000000000082</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>262.395</v>
+        <v>47.75</v>
       </c>
       <c r="F4" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -624,8 +624,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
-        </is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>-8.581999999999994</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -636,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -650,13 +653,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E5" t="n">
-        <v>87.76000000000001</v>
+        <v>57.3318839375</v>
       </c>
       <c r="F5" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -665,8 +668,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
-        </is>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>-8.997076187499971</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -677,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -691,13 +697,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>47.75</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -708,6 +714,9 @@
         <is>
           <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2.399999999999977</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -732,7 +741,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
         <v>65.33711741009385</v>
@@ -751,7 +760,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29.80253165610077</v>
+        <v>58.89847496525603</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>47.75</v>
+        <v>57.3318839375</v>
       </c>
       <c r="F4" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -624,11 +624,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-8.581999999999994</v>
+        <v>-8.997076187499971</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,13 +653,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>57.3318839375</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -668,11 +668,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-8.997076187499971</v>
+        <v>2.399999999999977</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>87.76000000000001</v>
+        <v>65.33711741009385</v>
       </c>
       <c r="F6" t="n">
-        <v>71.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -712,11 +712,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2.399999999999977</v>
+        <v>58.89847496525603</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
-        <v>65.33711741009385</v>
+        <v>47.7380487804878</v>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -756,11 +756,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>58.89847496525603</v>
+        <v>-8.581999999999994</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>262.395</v>
+        <v>28.565</v>
       </c>
       <c r="F3" t="n">
-        <v>75.3</v>
+        <v>80.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -580,22 +580,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2.910000000000082</v>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>increase toward target 15% of capital (core)</t>
+          <t>increase toward target 14% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,13 +606,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>57.3318839375</v>
+        <v>262.395</v>
       </c>
       <c r="F4" t="n">
-        <v>71.2</v>
+        <v>75.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -624,11 +621,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-8.997076187499971</v>
+        <v>5.385000000000105</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -639,7 +636,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,13 +650,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>87.76000000000001</v>
+        <v>57.3318839375</v>
       </c>
       <c r="F5" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -668,11 +665,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.399999999999977</v>
+        <v>-11.445328</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -683,7 +680,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -697,13 +694,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>65.33711741009385</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -712,11 +709,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>58.89847496525603</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -727,42 +724,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91.62</v>
+      </c>
+      <c r="F7" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>increase toward target 14% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65.33711741009385</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>76.77000532488064</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SPYD</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>82</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D9" t="n">
+        <v>78</v>
+      </c>
+      <c r="E9" t="n">
         <v>47.7380487804878</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F9" t="n">
         <v>70.5</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>-8.581999999999994</v>
-      </c>
-      <c r="L7" t="inlineStr">
+      <c r="K9" t="n">
+        <v>-13.5333951219512</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>increase toward target 15% of capital (core)</t>
         </is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>28.565</v>
+        <v>262.5885714285714</v>
       </c>
       <c r="F3" t="n">
-        <v>80.3</v>
+        <v>75.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -580,19 +580,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-24T13:36:39.185711+00:00</t>
-        </is>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5.385000000000105</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>increase toward target 14% of capital (core)</t>
+          <t>increase toward target 15% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -606,13 +609,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>262.395</v>
+        <v>57.29776973134329</v>
       </c>
       <c r="F4" t="n">
-        <v>75.3</v>
+        <v>71.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -621,11 +624,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5.385000000000105</v>
+        <v>-11.445328</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -636,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -650,13 +653,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>57.3318839375</v>
+        <v>65.53732330937287</v>
       </c>
       <c r="F5" t="n">
-        <v>71.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -665,11 +668,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-11.445328</v>
+        <v>76.77000532488064</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -694,10 +697,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" t="n">
-        <v>87.76000000000001</v>
+        <v>87.75837209302325</v>
       </c>
       <c r="F6" t="n">
         <v>71.8</v>
@@ -724,7 +727,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,13 +741,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>91.62</v>
+        <v>47.62732295033793</v>
       </c>
       <c r="F7" t="n">
-        <v>72.7</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -753,19 +756,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-24T13:36:39.185711+00:00</t>
-        </is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-13.5333951219512</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>increase toward target 14% of capital (core)</t>
+          <t>increase toward target 15% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -779,37 +785,45 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>65.33711741009385</v>
+        <v>28.565</v>
       </c>
       <c r="F8" t="n">
-        <v>75.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
-        </is>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:35:42.695537+00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>28.5882813</v>
       </c>
       <c r="K8" t="n">
-        <v>76.77000532488064</v>
+        <v>2.980006399999638</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>increase toward target 15% of capital (core)</t>
+          <t>increase toward target 14% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -823,30 +837,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>47.7380487804878</v>
+        <v>91.62</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>72.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
-        </is>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:35:42.695537+00:00</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>91.71641030000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-13.5333951219512</v>
+        <v>3.760001700000089</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>increase toward target 15% of capital (core)</t>
+          <t>increase toward target 14% of capital (core)</t>
         </is>
       </c>
     </row>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>HDV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -565,37 +565,45 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="E3" t="n">
-        <v>262.5885714285714</v>
+        <v>28.565</v>
       </c>
       <c r="F3" t="n">
-        <v>75.3</v>
+        <v>80.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
-        </is>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:35:42.695537+00:00</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>28.5882813</v>
       </c>
       <c r="K3" t="n">
-        <v>5.385000000000105</v>
+        <v>2.980006399999638</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>increase toward target 15% of capital (core)</t>
+          <t>increase toward target 14% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -609,37 +617,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>57.29776973134329</v>
+        <v>91.62</v>
       </c>
       <c r="F4" t="n">
-        <v>71.2</v>
+        <v>72.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
-        </is>
+          <t>2026-09-24T13:36:39.185711+00:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-25T13:35:42.695537+00:00</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>91.71641030000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-11.445328</v>
+        <v>3.760001700000089</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>increase toward target 15% of capital (core)</t>
+          <t>increase toward target 14% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -653,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>65.53732330937287</v>
+        <v>57.17463215</v>
       </c>
       <c r="F5" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -668,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>76.77000532488064</v>
+        <v>-11.445328</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -683,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -697,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>87.75837209302325</v>
+        <v>263.0988235294118</v>
       </c>
       <c r="F6" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -712,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.129999999999967</v>
+        <v>5.385000000000105</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -741,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E7" t="n">
-        <v>47.62732295033793</v>
+        <v>47.35987555998009</v>
       </c>
       <c r="F7" t="n">
         <v>70.5</v>
@@ -771,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -785,45 +801,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>28.565</v>
+        <v>87.6786274509804</v>
       </c>
       <c r="F8" t="n">
-        <v>80.3</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-24T13:36:39.185711+00:00</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-25T13:35:42.695537+00:00</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>28.5882813</v>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
       </c>
       <c r="K8" t="n">
-        <v>2.980006399999638</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>increase toward target 14% of capital (core)</t>
+          <t>increase toward target 15% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -837,38 +845,30 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>91.62</v>
+        <v>66.02438623576739</v>
       </c>
       <c r="F9" t="n">
-        <v>72.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-24T13:36:39.185711+00:00</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-09-25T13:35:42.695537+00:00</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>91.71641030000001</v>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
       </c>
       <c r="K9" t="n">
-        <v>3.760001700000089</v>
+        <v>76.77000532488064</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>increase toward target 14% of capital (core)</t>
+          <t>increase toward target 15% of capital (core)</t>
         </is>
       </c>
     </row>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E5" t="n">
-        <v>57.17463215</v>
+        <v>47.35987555998009</v>
       </c>
       <c r="F5" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-11.445328</v>
+        <v>-13.5333951219512</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>263.0988235294118</v>
+        <v>87.6786274509804</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>71.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.385000000000105</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>47.35987555998009</v>
+        <v>57.17463215</v>
       </c>
       <c r="F7" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-13.5333951219512</v>
+        <v>-12.17496015</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>87.6786274509804</v>
+        <v>263.0988235294118</v>
       </c>
       <c r="F8" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.129999999999967</v>
+        <v>9.181176470588298</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>66.02438623576739</v>
+        <v>66.05818341401334</v>
       </c>
       <c r="F9" t="n">
         <v>75.09999999999999</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>263.0988235294118</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F8" t="n">
         <v>75.3</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
         <v>66.05818341401334</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>76.77000532488064</v>
+        <v>79.5518219108673</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>66.05818341401334</v>
+        <v>66.0757866956192</v>
       </c>
       <c r="F9" t="n">
         <v>75.09999999999999</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>87.6786274509804</v>
+        <v>57.17463215</v>
       </c>
       <c r="F6" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.129999999999967</v>
+        <v>-12.17496015</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>57.17463215</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F7" t="n">
-        <v>71.2</v>
+        <v>75.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-12.17496015</v>
+        <v>9.181176470588298</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>263.203892733564</v>
+        <v>66.0757866956192</v>
       </c>
       <c r="F8" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>9.181176470588298</v>
+        <v>79.5518219108673</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>66.0757866956192</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>75.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>79.5518219108673</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>66.0757866956192</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>75.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>79.5518219108673</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
-        <v>87.64500000000001</v>
+        <v>66.07868540165474</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.129999999999967</v>
+        <v>79.5518219108673</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>263.203892733564</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>75.3</v>
+        <v>71.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9.181176470588298</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>87.64500000000001</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F8" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5.129999999999967</v>
+        <v>13.18228373702425</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
         <v>66.07868540165474</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>79.5518219108673</v>
+        <v>81.55813650921256</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="E5" t="n">
-        <v>47.35987555998009</v>
+        <v>57.17463215</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-13.5333951219512</v>
+        <v>-12.17496015</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>57.17463215</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-12.17496015</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>87.64500000000001</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5.129999999999967</v>
+        <v>13.18228373702425</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="E8" t="n">
-        <v>263.203892733564</v>
+        <v>46.16</v>
       </c>
       <c r="F8" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,8 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>13.18228373702425</v>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -845,7 +842,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
         <v>66.07868540165474</v>
@@ -864,9 +861,53 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>81.55813650921256</v>
+        <v>88.07076570590307</v>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>increase toward target 15% of capital (core)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SPYD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>99</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47.34088691796008</v>
+      </c>
+      <c r="F10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>-13.5333951219512</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>increase toward target 15% of capital (core)</t>
         </is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>57.17463215</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-12.17496015</v>
+        <v>5.129999999999967</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>87.64500000000001</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F6" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.129999999999967</v>
+        <v>13.18228373702425</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E7" t="n">
-        <v>263.203892733564</v>
+        <v>47.34088691796008</v>
       </c>
       <c r="F7" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>13.18228373702425</v>
+        <v>-13.5333951219512</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>46.16</v>
+        <v>57.164636748125</v>
       </c>
       <c r="F8" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,8 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
-        </is>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-12.17496015</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -828,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E9" t="n">
-        <v>66.07868540165474</v>
+        <v>46.15806122448979</v>
       </c>
       <c r="F9" t="n">
-        <v>75.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -857,11 +860,8 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>88.07076570590307</v>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>47.34088691796008</v>
+        <v>66.07868540165474</v>
       </c>
       <c r="F10" t="n">
-        <v>70.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-13.5333951219512</v>
+        <v>92.84208030424833</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>87.64500000000001</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F5" t="n">
-        <v>71.8</v>
+        <v>75.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5.129999999999967</v>
+        <v>13.18228373702425</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>263.203892733564</v>
+        <v>66.07868540165474</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>13.18228373702425</v>
+        <v>92.84208030424833</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E7" t="n">
-        <v>47.34088691796008</v>
+        <v>45.94219047619047</v>
       </c>
       <c r="F7" t="n">
         <v>70.5</v>
@@ -772,11 +772,8 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>-13.5333951219512</v>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -801,7 +798,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
         <v>57.164636748125</v>
@@ -820,7 +817,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-12.17496015</v>
+        <v>-12.624596898125</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +828,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +842,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>46.15806122448979</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,8 +857,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
-        </is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>5.292999999999964</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>66.07868540165474</v>
+        <v>47.34088691796008</v>
       </c>
       <c r="F10" t="n">
-        <v>75.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -901,11 +901,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>92.84208030424833</v>
+        <v>-15.19428203991129</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>66.07868540165474</v>
+        <v>57.164636748125</v>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>92.84208030424833</v>
+        <v>-12.624596898125</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E7" t="n">
-        <v>45.94219047619047</v>
+        <v>47.34088691796008</v>
       </c>
       <c r="F7" t="n">
         <v>70.5</v>
@@ -772,8 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
-        </is>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-15.19428203991129</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -784,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -798,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E8" t="n">
-        <v>57.164636748125</v>
+        <v>45.9079716981132</v>
       </c>
       <c r="F8" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -813,11 +816,8 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>-12.624596898125</v>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>87.64500000000001</v>
+        <v>66.07868540165474</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -857,11 +857,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5.292999999999964</v>
+        <v>98.49839490259359</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>47.34088691796008</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-15.19428203991129</v>
+        <v>6.422999999999959</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>47.34088691796008</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-15.19428203991129</v>
+        <v>6.422999999999959</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" t="n">
         <v>45.9079716981132</v>
@@ -818,6 +818,9 @@
         <is>
           <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-2.926971698113199</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -842,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>66.07868540165474</v>
+        <v>66.17013483972372</v>
       </c>
       <c r="F9" t="n">
         <v>75.09999999999999</v>
@@ -872,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -886,13 +889,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E10" t="n">
-        <v>87.64500000000001</v>
+        <v>47.34088691796008</v>
       </c>
       <c r="F10" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -905,7 +908,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.422999999999959</v>
+        <v>-16.20516895787137</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="E5" t="n">
-        <v>263.203892733564</v>
+        <v>45.9079716981132</v>
       </c>
       <c r="F5" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13.18228373702425</v>
+        <v>-17.13480188679241</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>57.164636748125</v>
+        <v>263.203892733564</v>
       </c>
       <c r="F6" t="n">
-        <v>71.2</v>
+        <v>75.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-12.624596898125</v>
+        <v>27.15339100346023</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>87.64500000000001</v>
+        <v>66.17013483972372</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.422999999999959</v>
+        <v>117.4579903834224</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>45.9079716981132</v>
+        <v>87.64500000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-2.926971698113199</v>
+        <v>16.63799999999992</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>66.17013483972372</v>
+        <v>57.164636748125</v>
       </c>
       <c r="F9" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>98.49839490259359</v>
+        <v>-13.52350714249999</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
         <v>47.34088691796008</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-16.20516895787137</v>
+        <v>-20.04782971175162</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>45.9079716981132</v>
+        <v>264.8392744377163</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>75.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-17T13:35:40.671604+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-17.13480188679241</v>
+        <v>27.15339100346023</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="E6" t="n">
-        <v>263.203892733564</v>
+        <v>45.8723223117787</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>70.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:40.671604+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>27.15339100346023</v>
+        <v>-17.13480188679241</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>66.17013483972372</v>
+        <v>66.31603426858071</v>
       </c>
       <c r="F7" t="n">
         <v>75.09999999999999</v>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>87.64500000000001</v>
+        <v>57.15826410935184</v>
       </c>
       <c r="F8" t="n">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.63799999999992</v>
+        <v>-13.52350714249999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>57.164636748125</v>
+        <v>87.89087755102041</v>
       </c>
       <c r="F9" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-13.52350714249999</v>
+        <v>16.63799999999992</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
-        <v>47.34088691796008</v>
+        <v>47.31558959887119</v>
       </c>
       <c r="F10" t="n">
         <v>70.5</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>264.8392744377163</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>27.15339100346023</v>
+        <v>45.5791165657439</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>45.8723223117787</v>
+        <v>66.31603426858071</v>
       </c>
       <c r="F6" t="n">
-        <v>70.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-17.13480188679241</v>
+        <v>134.165921846261</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E7" t="n">
-        <v>66.31603426858071</v>
+        <v>45.8723223117787</v>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>117.4579903834224</v>
+        <v>-22.70409113390723</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
         <v>57.15826410935184</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-13.52350714249999</v>
+        <v>-13.07856357990735</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
         <v>87.89087755102041</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.63799999999992</v>
+        <v>27.11624489795909</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
         <v>47.31558959887119</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-20.04782971175162</v>
+        <v>-20.86136730497877</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>264.8392744377163</v>
+        <v>266.1886947853591</v>
       </c>
       <c r="F5" t="n">
         <v>75.3</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>66.31603426858071</v>
+        <v>66.78358764835336</v>
       </c>
       <c r="F6" t="n">
         <v>75.09999999999999</v>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E7" t="n">
-        <v>45.8723223117787</v>
+        <v>45.78476103681992</v>
       </c>
       <c r="F7" t="n">
         <v>70.5</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>57.15826410935184</v>
+        <v>57.15612761012459</v>
       </c>
       <c r="F8" t="n">
         <v>71.2</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="n">
-        <v>87.89087755102041</v>
+        <v>88.11288254893795</v>
       </c>
       <c r="F9" t="n">
         <v>71.8</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
-        <v>47.31558959887119</v>
+        <v>47.2958568959093</v>
       </c>
       <c r="F10" t="n">
         <v>70.5</v>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>266.1886947853591</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>45.5791165657439</v>
+        <v>67.28042178038481</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>66.78358764835336</v>
+        <v>57.15612761012459</v>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>134.165921846261</v>
+        <v>-12.8430740204057</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
-        <v>45.78476103681992</v>
+        <v>66.78358764835336</v>
       </c>
       <c r="F7" t="n">
-        <v>70.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-22.70409113390723</v>
+        <v>167.7115712528476</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E8" t="n">
-        <v>57.15612761012459</v>
+        <v>45.78476103681992</v>
       </c>
       <c r="F8" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-13.07856357990735</v>
+        <v>-29.75265735482677</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
         <v>88.11288254893795</v>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>27.11624489795909</v>
+        <v>38.7304798000832</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
         <v>47.2958568959093</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-20.86136730497877</v>
+        <v>-21.19650868043458</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
-        <v>45.78476103681992</v>
+        <v>88.11288254893795</v>
       </c>
       <c r="F8" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-29.75265735482677</v>
+        <v>38.7304798000832</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="E9" t="n">
-        <v>88.11288254893795</v>
+        <v>47.2958568959093</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>38.7304798000832</v>
+        <v>-21.19650868043458</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E10" t="n">
-        <v>47.2958568959093</v>
+        <v>45.74328062024923</v>
       </c>
       <c r="F10" t="n">
         <v>70.5</v>
@@ -904,11 +904,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-21.19650868043458</v>
+        <v>-29.75265735482677</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>266.1886947853591</v>
+        <v>267.0825263612741</v>
       </c>
       <c r="F5" t="n">
         <v>75.3</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
-        <v>57.15612761012459</v>
+        <v>57.15582501209376</v>
       </c>
       <c r="F6" t="n">
         <v>71.2</v>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>66.78358764835336</v>
+        <v>88.34480571020578</v>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>167.7115712528476</v>
+        <v>38.7304798000832</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>88.11288254893795</v>
+        <v>67.16809147182012</v>
       </c>
       <c r="F8" t="n">
-        <v>71.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>38.7304798000832</v>
+        <v>167.7115712528476</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E9" t="n">
-        <v>47.2958568959093</v>
+        <v>45.68791754900164</v>
       </c>
       <c r="F9" t="n">
         <v>70.5</v>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-21.19650868043458</v>
+        <v>-29.75265735482677</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E10" t="n">
-        <v>45.74328062024923</v>
+        <v>47.31046073525325</v>
       </c>
       <c r="F10" t="n">
         <v>70.5</v>
@@ -904,11 +904,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-29.75265735482677</v>
+        <v>-21.19650868043458</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>267.0825263612741</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>67.28042178038481</v>
+        <v>82.89789541911068</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
         <v>57.15582501209376</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-12.8430740204057</v>
+        <v>-13.49054905668698</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="E7" t="n">
-        <v>88.34480571020578</v>
+        <v>45.68791754900164</v>
       </c>
       <c r="F7" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>38.7304798000832</v>
+        <v>-37.22672755083332</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
         <v>67.16809147182012</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>167.7115712528476</v>
+        <v>202.1792053655671</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>45.68791754900164</v>
+        <v>88.34480571020578</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-29.75265735482677</v>
+        <v>51.25086837967166</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E10" t="n">
         <v>47.31046073525325</v>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-21.19650868043458</v>
+        <v>-11.89927309195413</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E7" t="n">
-        <v>45.68791754900164</v>
+        <v>47.31046073525325</v>
       </c>
       <c r="F7" t="n">
         <v>70.5</v>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-37.22672755083332</v>
+        <v>-11.89927309195413</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>67.16809147182012</v>
+        <v>67.40248842275945</v>
       </c>
       <c r="F8" t="n">
         <v>75.09999999999999</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>88.34480571020578</v>
+        <v>88.43053892457648</v>
       </c>
       <c r="F9" t="n">
         <v>71.8</v>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E10" t="n">
-        <v>47.31046073525325</v>
+        <v>45.66695757303103</v>
       </c>
       <c r="F10" t="n">
         <v>70.5</v>
@@ -904,11 +904,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-11.89927309195413</v>
+        <v>-37.22672755083332</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E6" t="n">
-        <v>57.15582501209376</v>
+        <v>47.31046073525325</v>
       </c>
       <c r="F6" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-13.49054905668698</v>
+        <v>-11.89927309195413</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>47.31046073525325</v>
+        <v>67.40248842275945</v>
       </c>
       <c r="F7" t="n">
-        <v>70.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-11.89927309195413</v>
+        <v>202.1792053655671</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>67.40248842275945</v>
+        <v>88.43053892457648</v>
       </c>
       <c r="F8" t="n">
-        <v>75.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>202.1792053655671</v>
+        <v>51.25086837967166</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E9" t="n">
-        <v>88.43053892457648</v>
+        <v>45.66695757303103</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>51.25086837967166</v>
+        <v>-37.22672755083332</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>45.66695757303103</v>
+        <v>57.15582501209376</v>
       </c>
       <c r="F10" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -904,11 +904,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-37.22672755083332</v>
+        <v>-13.56627406878074</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>267.0825263612741</v>
+        <v>268.1611184636945</v>
       </c>
       <c r="F5" t="n">
         <v>75.3</v>
@@ -699,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>JEPI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>47.31046073525325</v>
+        <v>57.16156907414023</v>
       </c>
       <c r="F6" t="n">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -728,11 +728,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-09-04T13:35:33.221049+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>-11.89927309195413</v>
+        <v>-13.56627406878074</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>67.40248842275945</v>
+        <v>67.67141754548518</v>
       </c>
       <c r="F7" t="n">
         <v>75.09999999999999</v>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="E8" t="n">
-        <v>88.43053892457648</v>
+        <v>45.59311011744496</v>
       </c>
       <c r="F8" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>51.25086837967166</v>
+        <v>-37.22672755083332</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>45.66695757303103</v>
+        <v>88.54371736759343</v>
       </c>
       <c r="F9" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -860,11 +860,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-37.22672755083332</v>
+        <v>51.25086837967166</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JEPI</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E10" t="n">
-        <v>57.15582501209376</v>
+        <v>47.34949923862548</v>
       </c>
       <c r="F10" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -904,11 +904,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-04T13:35:33.221049+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-13.56627406878074</v>
+        <v>-11.89927309195413</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>

--- a/trade_journal_dividend.xlsx
+++ b/trade_journal_dividend.xlsx
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="E7" t="n">
-        <v>67.67141754548518</v>
+        <v>45.59311011744496</v>
       </c>
       <c r="F7" t="n">
-        <v>75.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-17T13:32:55.671253+00:00</t>
+          <t>2026-10-07T13:35:29.469982+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>202.1792053655671</v>
+        <v>-37.22672755083332</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>45.59311011744496</v>
+        <v>88.54371736759343</v>
       </c>
       <c r="F8" t="n">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -816,11 +816,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-07T13:35:29.469982+00:00</t>
+          <t>2026-09-18T13:35:43.767553+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-37.22672755083332</v>
+        <v>51.25086837967166</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SPYD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>88.54371736759343</v>
+        <v>47.34949923862548</v>
       </c>
       <c r="F9" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>51.25086837967166</v>
+        <v>-11.89927309195413</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPYD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -889,26 +889,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>47.34949923862548</v>
+        <v>67.67141754548518</v>
       </c>
       <c r="F10" t="n">
-        <v>70.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:43.767553+00:00</t>
-        </is>
+          <t>2026-08-17T13:32:55.671253+00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:35:36.669850+00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>76.0419</v>
       </c>
       <c r="K10" t="n">
-        <v>-11.89927309195413</v>
+        <v>729.5196000000004</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
